--- a/artfynd/A 59136-2024 artfynd.xlsx
+++ b/artfynd/A 59136-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1828,6 +1828,218 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121635263</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56568</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Slogmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>563736</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6698654</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121635268</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Slogmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>563788</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6698461</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59136-2024 artfynd.xlsx
+++ b/artfynd/A 59136-2024 artfynd.xlsx
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121635263</v>
+        <v>121635268</v>
       </c>
       <c r="B12" t="n">
-        <v>56568</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,46 +1842,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563736</v>
+        <v>563788</v>
       </c>
       <c r="R12" t="n">
-        <v>6698654</v>
+        <v>6698461</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121635268</v>
+        <v>121635263</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>56569</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,38 +1944,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563788</v>
+        <v>563736</v>
       </c>
       <c r="R13" t="n">
-        <v>6698461</v>
+        <v>6698654</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 59136-2024 artfynd.xlsx
+++ b/artfynd/A 59136-2024 artfynd.xlsx
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121635268</v>
+        <v>121635263</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,38 +1842,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563788</v>
+        <v>563736</v>
       </c>
       <c r="R12" t="n">
-        <v>6698461</v>
+        <v>6698654</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121635263</v>
+        <v>121635268</v>
       </c>
       <c r="B13" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,46 +1952,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563736</v>
+        <v>563788</v>
       </c>
       <c r="R13" t="n">
-        <v>6698654</v>
+        <v>6698461</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 59136-2024 artfynd.xlsx
+++ b/artfynd/A 59136-2024 artfynd.xlsx
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121635263</v>
+        <v>121635268</v>
       </c>
       <c r="B12" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,46 +1842,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563736</v>
+        <v>563788</v>
       </c>
       <c r="R12" t="n">
-        <v>6698654</v>
+        <v>6698461</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121635268</v>
+        <v>121635263</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,38 +1944,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563788</v>
+        <v>563736</v>
       </c>
       <c r="R13" t="n">
-        <v>6698461</v>
+        <v>6698654</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 59136-2024 artfynd.xlsx
+++ b/artfynd/A 59136-2024 artfynd.xlsx
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121635268</v>
+        <v>121635263</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>56577</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,38 +1842,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563788</v>
+        <v>563736</v>
       </c>
       <c r="R12" t="n">
-        <v>6698461</v>
+        <v>6698654</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121635263</v>
+        <v>121635268</v>
       </c>
       <c r="B13" t="n">
-        <v>56569</v>
+        <v>78629</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,46 +1952,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563736</v>
+        <v>563788</v>
       </c>
       <c r="R13" t="n">
-        <v>6698654</v>
+        <v>6698461</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 59136-2024 artfynd.xlsx
+++ b/artfynd/A 59136-2024 artfynd.xlsx
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121635263</v>
+        <v>121635268</v>
       </c>
       <c r="B12" t="n">
-        <v>56577</v>
+        <v>78631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,46 +1842,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563736</v>
+        <v>563788</v>
       </c>
       <c r="R12" t="n">
-        <v>6698654</v>
+        <v>6698461</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121635268</v>
+        <v>121635263</v>
       </c>
       <c r="B13" t="n">
-        <v>78629</v>
+        <v>56577</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,38 +1944,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563788</v>
+        <v>563736</v>
       </c>
       <c r="R13" t="n">
-        <v>6698461</v>
+        <v>6698654</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 59136-2024 artfynd.xlsx
+++ b/artfynd/A 59136-2024 artfynd.xlsx
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121635268</v>
+        <v>121635263</v>
       </c>
       <c r="B12" t="n">
-        <v>78631</v>
+        <v>56577</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,38 +1842,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563788</v>
+        <v>563736</v>
       </c>
       <c r="R12" t="n">
-        <v>6698461</v>
+        <v>6698654</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121635263</v>
+        <v>121635268</v>
       </c>
       <c r="B13" t="n">
-        <v>56577</v>
+        <v>78632</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,46 +1952,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563736</v>
+        <v>563788</v>
       </c>
       <c r="R13" t="n">
-        <v>6698654</v>
+        <v>6698461</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
